--- a/tests/fixtures/manual_spill_cache/input_copy.xlsx
+++ b/tests/fixtures/manual_spill_cache/input_copy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\pyOpenVBA\tests\fixtures\manual_spill_cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0F56A02-D057-4B31-A659-10C047F3B1C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A7EF294-1CFA-4DD2-A79E-D24074241491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="7200" windowHeight="4545" xr2:uid="{FC4AD28C-82BE-4E59-BDE7-8FC06975CBB6}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="7200" windowHeight="4545" xr2:uid="{C90BB75E-3D92-4AC3-92A3-1990254404F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -427,7 +427,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFEB2B40-1BFC-4C6A-A1E3-B0CFF002C3DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E918C874-463A-4A50-8ED3-893A8333F8D0}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -496,7 +496,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{895E0F28-0A7A-4784-8CCC-9277045D11FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC69E1B-8964-4A32-9330-204E2643C5AD}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
